--- a/api/Polla2026.xlsx
+++ b/api/Polla2026.xlsx
@@ -16,7 +16,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="112">
+  <si>
+    <t>Name:</t>
+  </si>
   <si>
     <t>Match</t>
   </si>
@@ -355,9 +358,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
@@ -374,6 +383,12 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -496,101 +511,108 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="69">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="5" fontId="3" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="5" fontId="3" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="6" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="6" fontId="3" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="6" fontId="3" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="7" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="7" fontId="3" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="7" fontId="3" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="8" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="8" fontId="3" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="8" fontId="3" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="5" fontId="4" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="5" fontId="4" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="9" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="9" fontId="3" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="9" fontId="3" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="9" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="10" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="10" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="10" fontId="3" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="10" fontId="3" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="10" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="6" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="6" fontId="4" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="6" fontId="4" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="11" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="11" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="11" fontId="3" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="11" fontId="3" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="11" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="7" fontId="4" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="7" fontId="4" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="12" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="12" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="12" fontId="3" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="12" fontId="3" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="12" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="8" fontId="4" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="8" fontId="4" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="13" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="13" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="13" fontId="3" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="13" fontId="3" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="13" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="9" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="9" fontId="4" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="9" fontId="4" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="14" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="14" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="14" fontId="3" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="14" fontId="3" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="14" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="10" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="10" fontId="4" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="10" fontId="4" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="11" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="11" fontId="4" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="11" fontId="4" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="12" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="12" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="12" fontId="4" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="12" fontId="4" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="12" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="13" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="13" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="13" fontId="4" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="13" fontId="4" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="13" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="14" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="14" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="14" fontId="4" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="14" fontId="4" numFmtId="18" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="14" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -613,7 +635,7 @@
     <xdr:ext cx="4572000" cy="647700"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png"/>
+        <xdr:cNvPr id="0" name="image10.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -641,7 +663,7 @@
     <xdr:ext cx="2886075" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png"/>
+        <xdr:cNvPr id="0" name="image5.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -669,7 +691,7 @@
     <xdr:ext cx="428625" cy="647700"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image12.png"/>
+        <xdr:cNvPr id="0" name="image9.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -697,7 +719,7 @@
     <xdr:ext cx="2552700" cy="1371600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image14.png"/>
+        <xdr:cNvPr id="0" name="image4.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -753,7 +775,7 @@
     <xdr:ext cx="2581275" cy="1390650"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.png"/>
+        <xdr:cNvPr id="0" name="image6.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -781,7 +803,7 @@
     <xdr:ext cx="2543175" cy="1371600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image8.png"/>
+        <xdr:cNvPr id="0" name="image3.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -837,7 +859,7 @@
     <xdr:ext cx="2571750" cy="1428750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image13.png"/>
+        <xdr:cNvPr id="0" name="image2.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -865,7 +887,7 @@
     <xdr:ext cx="2667000" cy="1428750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image9.png"/>
+        <xdr:cNvPr id="0" name="image14.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -893,7 +915,7 @@
     <xdr:ext cx="2552700" cy="1428750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.png"/>
+        <xdr:cNvPr id="0" name="image7.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -921,7 +943,7 @@
     <xdr:ext cx="2581275" cy="1447800"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image7.png"/>
+        <xdr:cNvPr id="0" name="image13.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -977,7 +999,7 @@
     <xdr:ext cx="2657475" cy="1438275"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.png"/>
+        <xdr:cNvPr id="0" name="image8.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1005,7 +1027,7 @@
     <xdr:ext cx="2581275" cy="1400175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image10.png"/>
+        <xdr:cNvPr id="0" name="image12.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1253,2324 +1275,2330 @@
     <col customWidth="1" min="24" max="26" width="8.71"/>
   </cols>
   <sheetData>
+    <row r="2">
+      <c r="S2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U2" s="2"/>
+    </row>
     <row r="5" ht="15.0" customHeight="1">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="G5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="I5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="J5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2" t="s">
+      <c r="K5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="N5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="O5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="P5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="Q5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="V5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="S5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="W5" s="1"/>
+      <c r="W5" s="3"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="1"/>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="3" t="s">
+      <c r="A6" s="3"/>
+      <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="1"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="3"/>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="4">
+      <c r="A7" s="3"/>
+      <c r="B7" s="6">
         <v>1.0</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="8">
         <v>46184.0</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="9">
         <v>0.625</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="8" t="s">
+      <c r="F7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="8" t="s">
+      <c r="G7" s="11"/>
+      <c r="H7" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="I7" s="11"/>
+      <c r="J7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="10"/>
-      <c r="M7" s="11">
+      <c r="K7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="12"/>
+      <c r="M7" s="13">
         <v>16.0</v>
       </c>
-      <c r="N7" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="O7" s="13">
+      <c r="N7" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7" s="15">
         <v>46188.0</v>
       </c>
-      <c r="P7" s="14">
+      <c r="P7" s="16">
         <v>0.875</v>
       </c>
-      <c r="Q7" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="R7" s="9"/>
-      <c r="S7" s="15" t="s">
+      <c r="Q7" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="T7" s="9"/>
-      <c r="U7" s="15" t="s">
+      <c r="R7" s="11"/>
+      <c r="S7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="V7" s="15" t="s">
+      <c r="T7" s="11"/>
+      <c r="U7" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="W7" s="1"/>
+      <c r="V7" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="W7" s="3"/>
     </row>
     <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="4">
+      <c r="A8" s="3"/>
+      <c r="B8" s="6">
         <v>2.0</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="8">
         <v>46184.0</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="9">
         <v>0.9166666666666666</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="8" t="s">
+      <c r="F8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="8" t="s">
+      <c r="G8" s="11"/>
+      <c r="H8" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="I8" s="11"/>
+      <c r="J8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="L8" s="10"/>
-      <c r="M8" s="11">
+      <c r="K8" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="12"/>
+      <c r="M8" s="13">
         <v>14.0</v>
       </c>
-      <c r="N8" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="O8" s="13">
+      <c r="N8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8" s="15">
         <v>46188.0</v>
       </c>
-      <c r="P8" s="14">
+      <c r="P8" s="16">
         <v>0.625</v>
       </c>
-      <c r="Q8" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="R8" s="9"/>
-      <c r="S8" s="15" t="s">
+      <c r="Q8" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="T8" s="9"/>
-      <c r="U8" s="15" t="s">
+      <c r="R8" s="11"/>
+      <c r="S8" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="V8" s="15" t="s">
+      <c r="T8" s="11"/>
+      <c r="U8" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="W8" s="1"/>
+      <c r="V8" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="W8" s="3"/>
     </row>
     <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="1"/>
-      <c r="B9" s="4">
+      <c r="A9" s="3"/>
+      <c r="B9" s="6">
         <v>25.0</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="8">
         <v>46191.0</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="9">
         <v>0.5</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="8" t="s">
+      <c r="F9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="L9" s="10"/>
-      <c r="M9" s="11">
+      <c r="K9" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="12"/>
+      <c r="M9" s="13">
         <v>38.0</v>
       </c>
-      <c r="N9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="O9" s="13">
+      <c r="N9" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="O9" s="15">
         <v>46194.0</v>
       </c>
-      <c r="P9" s="14">
+      <c r="P9" s="16">
         <v>0.625</v>
       </c>
-      <c r="Q9" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="R9" s="9"/>
-      <c r="S9" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="T9" s="9"/>
-      <c r="U9" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="V9" s="15" t="s">
+      <c r="Q9" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="R9" s="11"/>
+      <c r="S9" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="T9" s="11"/>
+      <c r="U9" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="W9" s="1"/>
+      <c r="V9" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="W9" s="3"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="4">
+      <c r="A10" s="3"/>
+      <c r="B10" s="6">
         <v>28.0</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="8">
         <v>46191.0</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="9">
         <v>0.875</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="K10" s="8" t="s">
+      <c r="F10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="L10" s="10"/>
-      <c r="M10" s="11">
+      <c r="K10" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="12"/>
+      <c r="M10" s="13">
         <v>40.0</v>
       </c>
-      <c r="N10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="O10" s="13">
+      <c r="N10" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="O10" s="15">
         <v>46194.0</v>
       </c>
-      <c r="P10" s="14">
+      <c r="P10" s="16">
         <v>0.875</v>
       </c>
-      <c r="Q10" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="R10" s="9"/>
-      <c r="S10" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="T10" s="9"/>
-      <c r="U10" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="V10" s="15" t="s">
+      <c r="Q10" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="R10" s="11"/>
+      <c r="S10" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="T10" s="11"/>
+      <c r="U10" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="W10" s="1"/>
+      <c r="V10" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="W10" s="3"/>
     </row>
     <row r="11" ht="15.0" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="4">
+      <c r="A11" s="3"/>
+      <c r="B11" s="6">
         <v>53.0</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="8">
         <v>46197.0</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="9">
         <v>0.875</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K11" s="8" t="s">
+      <c r="F11" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="L11" s="10"/>
-      <c r="M11" s="11">
+      <c r="K11" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="12"/>
+      <c r="M11" s="13">
         <v>65.0</v>
       </c>
-      <c r="N11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="O11" s="13">
+      <c r="N11" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="O11" s="15">
         <v>46199.0</v>
       </c>
-      <c r="P11" s="14">
+      <c r="P11" s="16">
         <v>0.9583333333333334</v>
       </c>
-      <c r="Q11" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="R11" s="9"/>
-      <c r="S11" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="T11" s="9"/>
-      <c r="U11" s="15" t="s">
+      <c r="Q11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="V11" s="15" t="s">
+      <c r="R11" s="11"/>
+      <c r="S11" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="T11" s="11"/>
+      <c r="U11" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="W11" s="1"/>
+      <c r="V11" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="W11" s="3"/>
     </row>
     <row r="12" ht="15.0" customHeight="1">
-      <c r="A12" s="1"/>
-      <c r="B12" s="4">
+      <c r="A12" s="3"/>
+      <c r="B12" s="6">
         <v>54.0</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="8">
+        <v>46197.0</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.875</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L12" s="12"/>
+      <c r="M12" s="13">
+        <v>66.0</v>
+      </c>
+      <c r="N12" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="O12" s="15">
+        <v>46199.0</v>
+      </c>
+      <c r="P12" s="16">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="Q12" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="R12" s="11"/>
+      <c r="S12" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T12" s="11"/>
+      <c r="U12" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="V12" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="6">
-        <v>46197.0</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.875</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="L12" s="10"/>
-      <c r="M12" s="11">
-        <v>66.0</v>
-      </c>
-      <c r="N12" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="O12" s="13">
-        <v>46199.0</v>
-      </c>
-      <c r="P12" s="14">
-        <v>0.9583333333333334</v>
-      </c>
-      <c r="Q12" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="R12" s="9"/>
-      <c r="S12" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="T12" s="9"/>
-      <c r="U12" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="V12" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="W12" s="1"/>
+      <c r="W12" s="3"/>
     </row>
     <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="16" t="s">
+      <c r="A13" s="3"/>
+      <c r="B13" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="N13" s="17"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="1"/>
-      <c r="X13" s="20"/>
-      <c r="Y13" s="20"/>
-      <c r="Z13" s="20"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="N13" s="19"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="12"/>
+      <c r="V13" s="12"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="23"/>
+      <c r="Y13" s="23"/>
+      <c r="Z13" s="23"/>
     </row>
     <row r="14" ht="15.0" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="21">
+      <c r="A14" s="3"/>
+      <c r="B14" s="24">
         <v>3.0</v>
       </c>
-      <c r="C14" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="23">
+      <c r="C14" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="26">
         <v>46185.0</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="27">
         <v>0.625</v>
       </c>
-      <c r="F14" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="25" t="s">
+      <c r="F14" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="I14" s="9"/>
-      <c r="J14" s="25" t="s">
+      <c r="G14" s="11"/>
+      <c r="H14" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="K14" s="25" t="s">
+      <c r="I14" s="11"/>
+      <c r="J14" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="L14" s="10"/>
-      <c r="M14" s="26">
+      <c r="K14" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="L14" s="12"/>
+      <c r="M14" s="29">
         <v>15.0</v>
       </c>
-      <c r="N14" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="O14" s="28">
+      <c r="N14" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14" s="31">
         <v>46188.0</v>
       </c>
-      <c r="P14" s="29">
+      <c r="P14" s="32">
         <v>0.75</v>
       </c>
-      <c r="Q14" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="R14" s="9"/>
-      <c r="S14" s="30" t="s">
+      <c r="Q14" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="T14" s="9"/>
-      <c r="U14" s="30" t="s">
+      <c r="R14" s="11"/>
+      <c r="S14" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="V14" s="30" t="s">
+      <c r="T14" s="11"/>
+      <c r="U14" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="W14" s="1"/>
+      <c r="V14" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="W14" s="3"/>
     </row>
     <row r="15" ht="15.0" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="21">
+      <c r="A15" s="3"/>
+      <c r="B15" s="24">
         <v>6.0</v>
       </c>
-      <c r="C15" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="23">
+      <c r="C15" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="26">
         <v>46186.0</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="27">
         <v>0.625</v>
       </c>
-      <c r="F15" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="25" t="s">
+      <c r="F15" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="I15" s="9"/>
-      <c r="J15" s="25" t="s">
+      <c r="G15" s="11"/>
+      <c r="H15" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="25" t="s">
+      <c r="I15" s="11"/>
+      <c r="J15" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="L15" s="10"/>
-      <c r="M15" s="26">
+      <c r="K15" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="L15" s="12"/>
+      <c r="M15" s="29">
         <v>13.0</v>
       </c>
-      <c r="N15" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="O15" s="28">
+      <c r="N15" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="O15" s="31">
         <v>46188.0</v>
       </c>
-      <c r="P15" s="29">
+      <c r="P15" s="32">
         <v>0.5</v>
       </c>
-      <c r="Q15" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="R15" s="9"/>
-      <c r="S15" s="30" t="s">
+      <c r="Q15" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="T15" s="9"/>
-      <c r="U15" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="V15" s="30" t="s">
+      <c r="R15" s="11"/>
+      <c r="S15" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="T15" s="11"/>
+      <c r="U15" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="W15" s="1"/>
+      <c r="V15" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="W15" s="3"/>
     </row>
     <row r="16" ht="15.0" customHeight="1">
-      <c r="A16" s="1"/>
-      <c r="B16" s="21">
+      <c r="A16" s="3"/>
+      <c r="B16" s="24">
         <v>26.0</v>
       </c>
-      <c r="C16" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="23">
+      <c r="C16" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="26">
         <v>46191.0</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="27">
         <v>0.625</v>
       </c>
-      <c r="F16" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" s="25" t="s">
+      <c r="F16" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="I16" s="11"/>
+      <c r="J16" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="L16" s="10"/>
-      <c r="M16" s="26">
+      <c r="K16" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" s="12"/>
+      <c r="M16" s="29">
         <v>39.0</v>
       </c>
-      <c r="N16" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="O16" s="28">
+      <c r="N16" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="O16" s="31">
         <v>46194.0</v>
       </c>
-      <c r="P16" s="29">
+      <c r="P16" s="32">
         <v>0.75</v>
       </c>
-      <c r="Q16" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="R16" s="9"/>
-      <c r="S16" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="T16" s="9"/>
-      <c r="U16" s="30" t="s">
+      <c r="Q16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="V16" s="30" t="s">
+      <c r="R16" s="11"/>
+      <c r="S16" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="T16" s="11"/>
+      <c r="U16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="W16" s="1"/>
+      <c r="V16" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="W16" s="3"/>
     </row>
     <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="21">
+      <c r="A17" s="3"/>
+      <c r="B17" s="24">
         <v>27.0</v>
       </c>
-      <c r="C17" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="23">
+      <c r="C17" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="26">
         <v>46191.0</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="27">
         <v>0.75</v>
       </c>
-      <c r="F17" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="25" t="s">
+      <c r="F17" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" s="11"/>
+      <c r="J17" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="L17" s="12"/>
+      <c r="M17" s="29">
+        <v>37.0</v>
+      </c>
+      <c r="N17" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="K17" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="L17" s="10"/>
-      <c r="M17" s="26">
-        <v>37.0</v>
-      </c>
-      <c r="N17" s="27" t="s">
+      <c r="O17" s="31">
+        <v>46194.0</v>
+      </c>
+      <c r="P17" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="Q17" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="R17" s="11"/>
+      <c r="S17" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="T17" s="11"/>
+      <c r="U17" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="V17" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="O17" s="28">
-        <v>46194.0</v>
-      </c>
-      <c r="P17" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="Q17" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="R17" s="9"/>
-      <c r="S17" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="T17" s="9"/>
-      <c r="U17" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="V17" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="W17" s="1"/>
+      <c r="W17" s="3"/>
     </row>
     <row r="18" ht="15.0" customHeight="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="21">
+      <c r="A18" s="3"/>
+      <c r="B18" s="24">
         <v>49.0</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="26">
+        <v>46197.0</v>
+      </c>
+      <c r="E18" s="27">
+        <v>0.625</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="11"/>
+      <c r="H18" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" s="11"/>
+      <c r="J18" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="23">
-        <v>46197.0</v>
-      </c>
-      <c r="E18" s="24">
-        <v>0.625</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="K18" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="L18" s="10"/>
-      <c r="M18" s="26">
+      <c r="L18" s="12"/>
+      <c r="M18" s="29">
         <v>63.0</v>
       </c>
-      <c r="N18" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="O18" s="28">
+      <c r="N18" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="O18" s="31">
         <v>46199.0</v>
       </c>
-      <c r="P18" s="29">
+      <c r="P18" s="32">
         <v>0.8333333333333334</v>
       </c>
-      <c r="Q18" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="R18" s="9"/>
-      <c r="S18" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="T18" s="9"/>
-      <c r="U18" s="30" t="s">
+      <c r="Q18" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="V18" s="30" t="s">
+      <c r="R18" s="11"/>
+      <c r="S18" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="T18" s="11"/>
+      <c r="U18" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="W18" s="1"/>
+      <c r="V18" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="W18" s="3"/>
     </row>
     <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="21">
+      <c r="A19" s="3"/>
+      <c r="B19" s="24">
         <v>50.0</v>
       </c>
-      <c r="C19" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="23">
+      <c r="C19" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="26">
         <v>46197.0</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="27">
         <v>0.625</v>
       </c>
-      <c r="F19" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="I19" s="9"/>
-      <c r="J19" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="K19" s="25" t="s">
+      <c r="F19" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="11"/>
+      <c r="H19" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="11"/>
+      <c r="J19" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="L19" s="10"/>
-      <c r="M19" s="26">
+      <c r="K19" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="L19" s="12"/>
+      <c r="M19" s="29">
         <v>64.0</v>
       </c>
-      <c r="N19" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="O19" s="28">
+      <c r="N19" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="O19" s="31">
         <v>46199.0</v>
       </c>
-      <c r="P19" s="29">
+      <c r="P19" s="32">
         <v>0.8333333333333334</v>
       </c>
-      <c r="Q19" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="R19" s="9"/>
-      <c r="S19" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="T19" s="9"/>
-      <c r="U19" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="V19" s="30" t="s">
+      <c r="Q19" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="R19" s="11"/>
+      <c r="S19" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="T19" s="11"/>
+      <c r="U19" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="W19" s="1"/>
+      <c r="V19" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="W19" s="3"/>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="1"/>
-      <c r="B20" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="16" t="s">
+      <c r="A20" s="3"/>
+      <c r="B20" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="N20" s="17"/>
-      <c r="O20" s="18"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="10"/>
-      <c r="S20" s="10"/>
-      <c r="T20" s="10"/>
-      <c r="U20" s="10"/>
-      <c r="V20" s="10"/>
-      <c r="W20" s="1"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="N20" s="19"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="22"/>
+      <c r="U20" s="12"/>
+      <c r="V20" s="12"/>
+      <c r="W20" s="3"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="1"/>
-      <c r="B21" s="31">
+      <c r="A21" s="3"/>
+      <c r="B21" s="34">
         <v>8.0</v>
       </c>
-      <c r="C21" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="33">
+      <c r="C21" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="36">
         <v>46186.0</v>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="37">
         <v>0.875</v>
       </c>
-      <c r="F21" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21" s="9"/>
-      <c r="H21" s="35" t="s">
+      <c r="F21" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="I21" s="9"/>
-      <c r="J21" s="35" t="s">
+      <c r="G21" s="11"/>
+      <c r="H21" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="K21" s="35" t="s">
+      <c r="I21" s="11"/>
+      <c r="J21" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="L21" s="10"/>
-      <c r="M21" s="36">
+      <c r="K21" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="L21" s="12"/>
+      <c r="M21" s="39">
         <v>18.0</v>
       </c>
-      <c r="N21" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="O21" s="38">
+      <c r="N21" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="O21" s="41">
         <v>46189.0</v>
       </c>
-      <c r="P21" s="39">
+      <c r="P21" s="42">
         <v>0.625</v>
       </c>
-      <c r="Q21" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="R21" s="9"/>
-      <c r="S21" s="40" t="s">
+      <c r="Q21" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="T21" s="9"/>
-      <c r="U21" s="40" t="s">
+      <c r="R21" s="11"/>
+      <c r="S21" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="V21" s="40" t="s">
+      <c r="T21" s="11"/>
+      <c r="U21" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="W21" s="1"/>
+      <c r="V21" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="W21" s="3"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="1"/>
-      <c r="B22" s="31">
+      <c r="A22" s="3"/>
+      <c r="B22" s="34">
         <v>7.0</v>
       </c>
-      <c r="C22" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="33">
+      <c r="C22" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="36">
         <v>46186.0</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="37">
         <v>0.75</v>
       </c>
-      <c r="F22" s="35" t="s">
+      <c r="F22" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="11"/>
+      <c r="H22" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="I22" s="11"/>
+      <c r="J22" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="K22" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="I22" s="9"/>
-      <c r="J22" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="K22" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="L22" s="10"/>
-      <c r="M22" s="36">
+      <c r="L22" s="12"/>
+      <c r="M22" s="39">
         <v>19.0</v>
       </c>
-      <c r="N22" s="37" t="s">
+      <c r="N22" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="O22" s="41">
+        <v>46189.0</v>
+      </c>
+      <c r="P22" s="42">
+        <v>0.75</v>
+      </c>
+      <c r="Q22" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="R22" s="11"/>
+      <c r="S22" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="T22" s="11"/>
+      <c r="U22" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="V22" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="O22" s="38">
-        <v>46189.0</v>
-      </c>
-      <c r="P22" s="39">
-        <v>0.75</v>
-      </c>
-      <c r="Q22" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="R22" s="9"/>
-      <c r="S22" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="T22" s="9"/>
-      <c r="U22" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="V22" s="40" t="s">
-        <v>64</v>
-      </c>
-      <c r="W22" s="1"/>
+      <c r="W22" s="3"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="1"/>
-      <c r="B23" s="31">
+      <c r="A23" s="3"/>
+      <c r="B23" s="34">
         <v>31.0</v>
       </c>
-      <c r="C23" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="33">
+      <c r="C23" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="36">
         <v>46192.0</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="37">
         <v>0.8541666666666666</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="11"/>
+      <c r="H23" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="I23" s="11"/>
+      <c r="J23" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="K23" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="L23" s="12"/>
+      <c r="M23" s="39">
+        <v>43.0</v>
+      </c>
+      <c r="N23" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="O23" s="41">
+        <v>46195.0</v>
+      </c>
+      <c r="P23" s="42">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="Q23" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="R23" s="11"/>
+      <c r="S23" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="T23" s="11"/>
+      <c r="U23" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="V23" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="G23" s="9"/>
-      <c r="H23" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="I23" s="9"/>
-      <c r="J23" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="K23" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="L23" s="10"/>
-      <c r="M23" s="36">
-        <v>43.0</v>
-      </c>
-      <c r="N23" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="O23" s="38">
-        <v>46195.0</v>
-      </c>
-      <c r="P23" s="39">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="Q23" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="R23" s="9"/>
-      <c r="S23" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="T23" s="9"/>
-      <c r="U23" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="V23" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="W23" s="1"/>
+      <c r="W23" s="3"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="B24" s="31">
+      <c r="A24" s="3"/>
+      <c r="B24" s="34">
         <v>30.0</v>
       </c>
-      <c r="C24" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="33">
+      <c r="C24" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="36">
         <v>46192.0</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="37">
         <v>0.75</v>
       </c>
-      <c r="F24" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="I24" s="9"/>
-      <c r="J24" s="35" t="s">
+      <c r="F24" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="K24" s="35" t="s">
+      <c r="G24" s="11"/>
+      <c r="H24" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="I24" s="11"/>
+      <c r="J24" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="L24" s="10"/>
-      <c r="M24" s="36">
+      <c r="K24" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="L24" s="12"/>
+      <c r="M24" s="39">
         <v>42.0</v>
       </c>
-      <c r="N24" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="O24" s="38">
+      <c r="N24" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="O24" s="41">
         <v>46195.0</v>
       </c>
-      <c r="P24" s="39">
+      <c r="P24" s="42">
         <v>0.7083333333333334</v>
       </c>
-      <c r="Q24" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="R24" s="9"/>
-      <c r="S24" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="T24" s="9"/>
-      <c r="U24" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="V24" s="40" t="s">
+      <c r="Q24" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="R24" s="11"/>
+      <c r="S24" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="T24" s="11"/>
+      <c r="U24" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="W24" s="1"/>
+      <c r="V24" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="W24" s="3"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="1"/>
-      <c r="B25" s="31">
+      <c r="A25" s="3"/>
+      <c r="B25" s="34">
         <v>51.0</v>
       </c>
-      <c r="C25" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" s="33">
+      <c r="C25" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="36">
         <v>46197.0</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="37">
         <v>0.75</v>
       </c>
-      <c r="F25" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="I25" s="9"/>
-      <c r="J25" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="K25" s="35" t="s">
+      <c r="F25" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" s="11"/>
+      <c r="H25" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="I25" s="11"/>
+      <c r="J25" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="L25" s="10"/>
-      <c r="M25" s="36">
+      <c r="K25" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="L25" s="12"/>
+      <c r="M25" s="39">
         <v>61.0</v>
       </c>
-      <c r="N25" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="O25" s="38">
+      <c r="N25" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="O25" s="41">
         <v>46199.0</v>
       </c>
-      <c r="P25" s="39">
+      <c r="P25" s="42">
         <v>0.625</v>
       </c>
-      <c r="Q25" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="R25" s="9"/>
-      <c r="S25" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="T25" s="9"/>
-      <c r="U25" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="V25" s="40" t="s">
+      <c r="Q25" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="R25" s="11"/>
+      <c r="S25" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="T25" s="11"/>
+      <c r="U25" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="W25" s="1"/>
+      <c r="V25" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="W25" s="3"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="1"/>
-      <c r="B26" s="31">
+      <c r="A26" s="3"/>
+      <c r="B26" s="34">
         <v>52.0</v>
       </c>
-      <c r="C26" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" s="33">
+      <c r="C26" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="36">
         <v>46197.0</v>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="37">
         <v>0.75</v>
       </c>
-      <c r="F26" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="9"/>
-      <c r="H26" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="I26" s="9"/>
-      <c r="J26" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="K26" s="35" t="s">
+      <c r="F26" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="G26" s="11"/>
+      <c r="H26" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="I26" s="11"/>
+      <c r="J26" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="L26" s="10"/>
-      <c r="M26" s="36">
+      <c r="K26" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="L26" s="12"/>
+      <c r="M26" s="39">
         <v>62.0</v>
       </c>
-      <c r="N26" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="O26" s="38">
+      <c r="N26" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="O26" s="41">
         <v>46199.0</v>
       </c>
-      <c r="P26" s="39">
+      <c r="P26" s="42">
         <v>0.625</v>
       </c>
-      <c r="Q26" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="R26" s="9"/>
-      <c r="S26" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="T26" s="9"/>
-      <c r="U26" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="V26" s="40" t="s">
+      <c r="Q26" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="R26" s="11"/>
+      <c r="S26" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="T26" s="11"/>
+      <c r="U26" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="W26" s="1"/>
+      <c r="V26" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="W26" s="3"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="16" t="s">
+      <c r="A27" s="3"/>
+      <c r="B27" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="N27" s="17"/>
-      <c r="O27" s="18"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="10"/>
-      <c r="R27" s="10"/>
-      <c r="S27" s="10"/>
-      <c r="T27" s="10"/>
-      <c r="U27" s="10"/>
-      <c r="V27" s="10"/>
-      <c r="W27" s="1"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="N27" s="19"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="22"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="22"/>
+      <c r="U27" s="12"/>
+      <c r="V27" s="12"/>
+      <c r="W27" s="3"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="1"/>
-      <c r="B28" s="41">
+      <c r="A28" s="3"/>
+      <c r="B28" s="44">
         <v>4.0</v>
       </c>
-      <c r="C28" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="43">
+      <c r="C28" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" s="46">
         <v>46185.0</v>
       </c>
-      <c r="E28" s="44">
+      <c r="E28" s="47">
         <v>0.875</v>
       </c>
-      <c r="F28" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="G28" s="9"/>
-      <c r="H28" s="45" t="s">
+      <c r="F28" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="I28" s="9"/>
-      <c r="J28" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="K28" s="45" t="s">
+      <c r="G28" s="11"/>
+      <c r="H28" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="I28" s="11"/>
+      <c r="J28" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="L28" s="10"/>
-      <c r="M28" s="46">
+      <c r="K28" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" s="12"/>
+      <c r="M28" s="49">
         <v>20.0</v>
       </c>
-      <c r="N28" s="47" t="s">
-        <v>65</v>
-      </c>
-      <c r="O28" s="48">
+      <c r="N28" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="O28" s="51">
         <v>46189.0</v>
       </c>
-      <c r="P28" s="49">
+      <c r="P28" s="52">
         <v>0.875</v>
       </c>
-      <c r="Q28" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="R28" s="9"/>
-      <c r="S28" s="50" t="s">
+      <c r="Q28" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="T28" s="9"/>
-      <c r="U28" s="50" t="s">
+      <c r="R28" s="11"/>
+      <c r="S28" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="V28" s="50" t="s">
+      <c r="T28" s="11"/>
+      <c r="U28" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="W28" s="1"/>
+      <c r="V28" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="W28" s="3"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="1"/>
-      <c r="B29" s="41">
+      <c r="A29" s="3"/>
+      <c r="B29" s="44">
         <v>5.0</v>
       </c>
-      <c r="C29" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" s="43">
+      <c r="C29" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" s="46">
         <v>46186.0</v>
       </c>
-      <c r="E29" s="44">
+      <c r="E29" s="47">
         <v>0.0</v>
       </c>
-      <c r="F29" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="G29" s="9"/>
-      <c r="H29" s="45" t="s">
+      <c r="F29" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="I29" s="9"/>
-      <c r="J29" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="K29" s="45" t="s">
+      <c r="G29" s="11"/>
+      <c r="H29" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="I29" s="11"/>
+      <c r="J29" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="L29" s="10"/>
-      <c r="M29" s="46">
+      <c r="K29" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="L29" s="12"/>
+      <c r="M29" s="49">
         <v>17.0</v>
       </c>
-      <c r="N29" s="47" t="s">
-        <v>65</v>
-      </c>
-      <c r="O29" s="48">
+      <c r="N29" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="O29" s="51">
         <v>46189.0</v>
       </c>
-      <c r="P29" s="49">
+      <c r="P29" s="52">
         <v>0.0</v>
       </c>
-      <c r="Q29" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="R29" s="9"/>
-      <c r="S29" s="50" t="s">
+      <c r="Q29" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="T29" s="9"/>
-      <c r="U29" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="V29" s="50" t="s">
+      <c r="R29" s="11"/>
+      <c r="S29" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="T29" s="11"/>
+      <c r="U29" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="W29" s="1"/>
+      <c r="V29" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="W29" s="3"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="1"/>
-      <c r="B30" s="41">
+      <c r="A30" s="3"/>
+      <c r="B30" s="44">
         <v>32.0</v>
       </c>
-      <c r="C30" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" s="43">
+      <c r="C30" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="46">
         <v>46192.0</v>
       </c>
-      <c r="E30" s="44">
+      <c r="E30" s="47">
         <v>0.9583333333333334</v>
       </c>
-      <c r="F30" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="G30" s="9"/>
-      <c r="H30" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="I30" s="9"/>
-      <c r="J30" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="K30" s="45" t="s">
+      <c r="F30" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="G30" s="11"/>
+      <c r="H30" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="I30" s="11"/>
+      <c r="J30" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="L30" s="10"/>
-      <c r="M30" s="46">
+      <c r="K30" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="L30" s="12"/>
+      <c r="M30" s="49">
         <v>41.0</v>
       </c>
-      <c r="N30" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="O30" s="48">
+      <c r="N30" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="O30" s="51">
         <v>46195.0</v>
       </c>
-      <c r="P30" s="49">
+      <c r="P30" s="52">
         <v>0.5416666666666666</v>
       </c>
-      <c r="Q30" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="R30" s="9"/>
-      <c r="S30" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="T30" s="9"/>
-      <c r="U30" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="V30" s="50" t="s">
+      <c r="Q30" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="R30" s="11"/>
+      <c r="S30" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="T30" s="11"/>
+      <c r="U30" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="W30" s="1"/>
+      <c r="V30" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="W30" s="3"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="1"/>
-      <c r="B31" s="41">
+      <c r="A31" s="3"/>
+      <c r="B31" s="44">
         <v>29.0</v>
       </c>
-      <c r="C31" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="43">
+      <c r="C31" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="46">
         <v>46192.0</v>
       </c>
-      <c r="E31" s="44">
+      <c r="E31" s="47">
         <v>0.625</v>
       </c>
-      <c r="F31" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="G31" s="9"/>
-      <c r="H31" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="I31" s="9"/>
-      <c r="J31" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="K31" s="45" t="s">
+      <c r="F31" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="G31" s="11"/>
+      <c r="H31" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="I31" s="11"/>
+      <c r="J31" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="L31" s="10"/>
-      <c r="M31" s="46">
+      <c r="K31" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="L31" s="12"/>
+      <c r="M31" s="49">
         <v>44.0</v>
       </c>
-      <c r="N31" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="O31" s="48">
+      <c r="N31" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="O31" s="51">
         <v>46195.0</v>
       </c>
-      <c r="P31" s="49">
+      <c r="P31" s="52">
         <v>0.9583333333333334</v>
       </c>
-      <c r="Q31" s="50" t="s">
-        <v>87</v>
-      </c>
-      <c r="R31" s="9"/>
-      <c r="S31" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="T31" s="9"/>
-      <c r="U31" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="V31" s="50" t="s">
+      <c r="Q31" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="R31" s="11"/>
+      <c r="S31" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="T31" s="11"/>
+      <c r="U31" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="W31" s="1"/>
+      <c r="V31" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="W31" s="3"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="1"/>
-      <c r="B32" s="41">
+      <c r="A32" s="3"/>
+      <c r="B32" s="44">
         <v>59.0</v>
       </c>
-      <c r="C32" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="43">
+      <c r="C32" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="46">
         <v>46198.0</v>
       </c>
-      <c r="E32" s="44">
+      <c r="E32" s="47">
         <v>0.9166666666666666</v>
       </c>
-      <c r="F32" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="I32" s="9"/>
-      <c r="J32" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="K32" s="45" t="s">
+      <c r="F32" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="G32" s="11"/>
+      <c r="H32" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="I32" s="11"/>
+      <c r="J32" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="L32" s="10"/>
-      <c r="M32" s="46">
+      <c r="K32" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" s="12"/>
+      <c r="M32" s="49">
         <v>71.0</v>
       </c>
-      <c r="N32" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="O32" s="48">
+      <c r="N32" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="O32" s="51">
         <v>46200.0</v>
       </c>
-      <c r="P32" s="49">
+      <c r="P32" s="52">
         <v>0.9166666666666666</v>
       </c>
-      <c r="Q32" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="R32" s="9"/>
-      <c r="S32" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="T32" s="9"/>
-      <c r="U32" s="50" t="s">
+      <c r="Q32" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="V32" s="50" t="s">
+      <c r="R32" s="11"/>
+      <c r="S32" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="T32" s="11"/>
+      <c r="U32" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="W32" s="1"/>
+      <c r="V32" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="W32" s="3"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="1"/>
-      <c r="B33" s="41">
+      <c r="A33" s="3"/>
+      <c r="B33" s="44">
         <v>60.0</v>
       </c>
-      <c r="C33" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="43">
+      <c r="C33" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="46">
         <v>46198.0</v>
       </c>
-      <c r="E33" s="44">
+      <c r="E33" s="47">
         <v>0.9166666666666666</v>
       </c>
-      <c r="F33" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="G33" s="9"/>
-      <c r="H33" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="I33" s="9"/>
-      <c r="J33" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="K33" s="45" t="s">
+      <c r="F33" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="G33" s="11"/>
+      <c r="H33" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="I33" s="11"/>
+      <c r="J33" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="L33" s="10"/>
-      <c r="M33" s="46">
+      <c r="K33" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="L33" s="12"/>
+      <c r="M33" s="49">
         <v>72.0</v>
       </c>
-      <c r="N33" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="O33" s="48">
+      <c r="N33" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="O33" s="51">
         <v>46200.0</v>
       </c>
-      <c r="P33" s="49">
+      <c r="P33" s="52">
         <v>0.9166666666666666</v>
       </c>
-      <c r="Q33" s="50" t="s">
-        <v>87</v>
-      </c>
-      <c r="R33" s="9"/>
-      <c r="S33" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="T33" s="9"/>
-      <c r="U33" s="50" t="s">
+      <c r="Q33" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="V33" s="50" t="s">
+      <c r="R33" s="11"/>
+      <c r="S33" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="T33" s="11"/>
+      <c r="U33" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="W33" s="1"/>
+      <c r="V33" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="W33" s="3"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="1"/>
-      <c r="B34" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="16" t="s">
+      <c r="A34" s="3"/>
+      <c r="B34" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="N34" s="17"/>
-      <c r="O34" s="18"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="10"/>
-      <c r="R34" s="10"/>
-      <c r="S34" s="10"/>
-      <c r="T34" s="10"/>
-      <c r="U34" s="10"/>
-      <c r="V34" s="10"/>
-      <c r="W34" s="1"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="N34" s="19"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="21"/>
+      <c r="Q34" s="12"/>
+      <c r="R34" s="22"/>
+      <c r="S34" s="12"/>
+      <c r="T34" s="22"/>
+      <c r="U34" s="12"/>
+      <c r="V34" s="12"/>
+      <c r="W34" s="3"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="1"/>
-      <c r="B35" s="51">
+      <c r="A35" s="3"/>
+      <c r="B35" s="54">
         <v>11.0</v>
       </c>
-      <c r="C35" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="D35" s="53">
+      <c r="C35" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="56">
         <v>46187.0</v>
       </c>
-      <c r="E35" s="54">
+      <c r="E35" s="57">
         <v>0.7916666666666666</v>
       </c>
-      <c r="F35" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="G35" s="9"/>
-      <c r="H35" s="55" t="s">
+      <c r="F35" s="58" t="s">
         <v>93</v>
       </c>
-      <c r="I35" s="9"/>
-      <c r="J35" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="K35" s="55" t="s">
+      <c r="G35" s="11"/>
+      <c r="H35" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="I35" s="11"/>
+      <c r="J35" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="L35" s="10"/>
-      <c r="M35" s="21">
+      <c r="K35" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="L35" s="12"/>
+      <c r="M35" s="24">
         <v>21.0</v>
       </c>
-      <c r="N35" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="O35" s="23">
+      <c r="N35" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="O35" s="26">
         <v>46190.0</v>
       </c>
-      <c r="P35" s="24">
+      <c r="P35" s="27">
         <v>0.5416666666666666</v>
       </c>
-      <c r="Q35" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="R35" s="9"/>
-      <c r="S35" s="25" t="s">
+      <c r="Q35" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="T35" s="9"/>
-      <c r="U35" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="V35" s="25" t="s">
+      <c r="R35" s="11"/>
+      <c r="S35" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="T35" s="11"/>
+      <c r="U35" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="W35" s="1"/>
+      <c r="V35" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="W35" s="3"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="1"/>
-      <c r="B36" s="51">
+      <c r="A36" s="3"/>
+      <c r="B36" s="54">
         <v>9.0</v>
       </c>
-      <c r="C36" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="D36" s="53">
+      <c r="C36" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="56">
         <v>46187.0</v>
       </c>
-      <c r="E36" s="54">
+      <c r="E36" s="57">
         <v>0.5416666666666666</v>
       </c>
-      <c r="F36" s="55" t="s">
-        <v>96</v>
-      </c>
-      <c r="G36" s="9"/>
-      <c r="H36" s="55" t="s">
+      <c r="F36" s="58" t="s">
         <v>97</v>
       </c>
-      <c r="I36" s="9"/>
-      <c r="J36" s="55" t="s">
-        <v>57</v>
-      </c>
-      <c r="K36" s="55" t="s">
+      <c r="G36" s="11"/>
+      <c r="H36" s="58" t="s">
+        <v>98</v>
+      </c>
+      <c r="I36" s="11"/>
+      <c r="J36" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="L36" s="10"/>
-      <c r="M36" s="21">
+      <c r="K36" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="L36" s="12"/>
+      <c r="M36" s="24">
         <v>24.0</v>
       </c>
-      <c r="N36" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="O36" s="23">
+      <c r="N36" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="O36" s="26">
         <v>46190.0</v>
       </c>
-      <c r="P36" s="24">
+      <c r="P36" s="27">
         <v>0.9166666666666666</v>
       </c>
-      <c r="Q36" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="R36" s="9"/>
-      <c r="S36" s="25" t="s">
+      <c r="Q36" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="T36" s="9"/>
-      <c r="U36" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="V36" s="25" t="s">
+      <c r="R36" s="11"/>
+      <c r="S36" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="T36" s="11"/>
+      <c r="U36" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="W36" s="1"/>
+      <c r="V36" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="W36" s="3"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="1"/>
-      <c r="B37" s="51">
+      <c r="A37" s="3"/>
+      <c r="B37" s="54">
         <v>35.0</v>
       </c>
-      <c r="C37" s="52" t="s">
-        <v>50</v>
-      </c>
-      <c r="D37" s="53">
+      <c r="C37" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" s="56">
         <v>46193.0</v>
       </c>
-      <c r="E37" s="54">
+      <c r="E37" s="57">
         <v>0.6666666666666666</v>
       </c>
-      <c r="F37" s="55" t="s">
-        <v>96</v>
-      </c>
-      <c r="G37" s="9"/>
-      <c r="H37" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="I37" s="9"/>
-      <c r="J37" s="55" t="s">
-        <v>44</v>
-      </c>
-      <c r="K37" s="55" t="s">
+      <c r="F37" s="58" t="s">
+        <v>97</v>
+      </c>
+      <c r="G37" s="11"/>
+      <c r="H37" s="58" t="s">
+        <v>93</v>
+      </c>
+      <c r="I37" s="11"/>
+      <c r="J37" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="L37" s="10"/>
-      <c r="M37" s="21">
+      <c r="K37" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="L37" s="12"/>
+      <c r="M37" s="24">
         <v>45.0</v>
       </c>
-      <c r="N37" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="O37" s="23">
+      <c r="N37" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="O37" s="26">
         <v>46196.0</v>
       </c>
-      <c r="P37" s="24">
+      <c r="P37" s="27">
         <v>0.5416666666666666</v>
       </c>
-      <c r="Q37" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="R37" s="9"/>
-      <c r="S37" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="T37" s="9"/>
-      <c r="U37" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="V37" s="25" t="s">
+      <c r="Q37" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="R37" s="11"/>
+      <c r="S37" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="T37" s="11"/>
+      <c r="U37" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="W37" s="1"/>
+      <c r="V37" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="W37" s="3"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="1"/>
-      <c r="B38" s="51">
+      <c r="A38" s="3"/>
+      <c r="B38" s="54">
         <v>36.0</v>
       </c>
-      <c r="C38" s="52" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38" s="53">
+      <c r="C38" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="D38" s="56">
         <v>46193.0</v>
       </c>
-      <c r="E38" s="54">
+      <c r="E38" s="57">
         <v>0.8333333333333334</v>
       </c>
-      <c r="F38" s="55" t="s">
-        <v>93</v>
-      </c>
-      <c r="G38" s="9"/>
-      <c r="H38" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="I38" s="9"/>
-      <c r="J38" s="55" t="s">
-        <v>82</v>
-      </c>
-      <c r="K38" s="55" t="s">
+      <c r="F38" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="G38" s="11"/>
+      <c r="H38" s="58" t="s">
+        <v>98</v>
+      </c>
+      <c r="I38" s="11"/>
+      <c r="J38" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="L38" s="10"/>
-      <c r="M38" s="21">
+      <c r="K38" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="L38" s="12"/>
+      <c r="M38" s="24">
         <v>48.0</v>
       </c>
-      <c r="N38" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="O38" s="23">
+      <c r="N38" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="O38" s="26">
         <v>46196.0</v>
       </c>
-      <c r="P38" s="24">
+      <c r="P38" s="27">
         <v>0.9166666666666666</v>
       </c>
-      <c r="Q38" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="R38" s="9"/>
-      <c r="S38" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="T38" s="9"/>
-      <c r="U38" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="V38" s="25" t="s">
+      <c r="Q38" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="R38" s="11"/>
+      <c r="S38" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="T38" s="11"/>
+      <c r="U38" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="W38" s="1"/>
+      <c r="V38" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="W38" s="3"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="1"/>
-      <c r="B39" s="51">
+      <c r="A39" s="3"/>
+      <c r="B39" s="54">
         <v>55.0</v>
       </c>
-      <c r="C39" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="53">
+      <c r="C39" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="56">
         <v>46198.0</v>
       </c>
-      <c r="E39" s="54">
+      <c r="E39" s="57">
         <v>0.6666666666666666</v>
       </c>
-      <c r="F39" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="G39" s="9"/>
-      <c r="H39" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="I39" s="9"/>
-      <c r="J39" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="K39" s="55" t="s">
+      <c r="F39" s="58" t="s">
+        <v>98</v>
+      </c>
+      <c r="G39" s="11"/>
+      <c r="H39" s="58" t="s">
+        <v>93</v>
+      </c>
+      <c r="I39" s="11"/>
+      <c r="J39" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="L39" s="10"/>
-      <c r="M39" s="21">
+      <c r="K39" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="L39" s="12"/>
+      <c r="M39" s="24">
         <v>69.0</v>
       </c>
-      <c r="N39" s="22" t="s">
+      <c r="N39" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="O39" s="26">
+        <v>46200.0</v>
+      </c>
+      <c r="P39" s="27">
+        <v>0.8125</v>
+      </c>
+      <c r="Q39" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="R39" s="11"/>
+      <c r="S39" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="T39" s="11"/>
+      <c r="U39" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="V39" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="O39" s="23">
-        <v>46200.0</v>
-      </c>
-      <c r="P39" s="24">
-        <v>0.8125</v>
-      </c>
-      <c r="Q39" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="R39" s="9"/>
-      <c r="S39" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="T39" s="9"/>
-      <c r="U39" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="V39" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="W39" s="1"/>
+      <c r="W39" s="3"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="1"/>
-      <c r="B40" s="51">
+      <c r="A40" s="3"/>
+      <c r="B40" s="54">
         <v>56.0</v>
       </c>
-      <c r="C40" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="53">
+      <c r="C40" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="56">
         <v>46198.0</v>
       </c>
-      <c r="E40" s="54">
+      <c r="E40" s="57">
         <v>0.6666666666666666</v>
       </c>
-      <c r="F40" s="55" t="s">
-        <v>93</v>
-      </c>
-      <c r="G40" s="9"/>
-      <c r="H40" s="55" t="s">
+      <c r="F40" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="G40" s="11"/>
+      <c r="H40" s="58" t="s">
+        <v>97</v>
+      </c>
+      <c r="I40" s="11"/>
+      <c r="J40" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="K40" s="58" t="s">
+        <v>70</v>
+      </c>
+      <c r="L40" s="12"/>
+      <c r="M40" s="24">
+        <v>70.0</v>
+      </c>
+      <c r="N40" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="O40" s="26">
+        <v>46200.0</v>
+      </c>
+      <c r="P40" s="27">
+        <v>0.8125</v>
+      </c>
+      <c r="Q40" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="I40" s="9"/>
-      <c r="J40" s="55" t="s">
-        <v>68</v>
-      </c>
-      <c r="K40" s="55" t="s">
-        <v>69</v>
-      </c>
-      <c r="L40" s="10"/>
-      <c r="M40" s="21">
-        <v>70.0</v>
-      </c>
-      <c r="N40" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="O40" s="23">
-        <v>46200.0</v>
-      </c>
-      <c r="P40" s="24">
-        <v>0.8125</v>
-      </c>
-      <c r="Q40" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="R40" s="9"/>
-      <c r="S40" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="T40" s="9"/>
-      <c r="U40" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="V40" s="25" t="s">
+      <c r="R40" s="11"/>
+      <c r="S40" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="T40" s="11"/>
+      <c r="U40" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="W40" s="1"/>
+      <c r="V40" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="W40" s="3"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="1"/>
-      <c r="B41" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="C41" s="17"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="16" t="s">
+      <c r="A41" s="3"/>
+      <c r="B41" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="N41" s="17"/>
-      <c r="O41" s="18"/>
-      <c r="P41" s="19"/>
-      <c r="Q41" s="10"/>
-      <c r="R41" s="10"/>
-      <c r="S41" s="10"/>
-      <c r="T41" s="10"/>
-      <c r="U41" s="10"/>
-      <c r="V41" s="10"/>
-      <c r="W41" s="1"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
+      <c r="L41" s="12"/>
+      <c r="M41" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="N41" s="19"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="21"/>
+      <c r="Q41" s="12"/>
+      <c r="R41" s="22"/>
+      <c r="S41" s="12"/>
+      <c r="T41" s="22"/>
+      <c r="U41" s="12"/>
+      <c r="V41" s="12"/>
+      <c r="W41" s="3"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="1"/>
-      <c r="B42" s="56">
+      <c r="A42" s="3"/>
+      <c r="B42" s="59">
         <v>10.0</v>
       </c>
-      <c r="C42" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="D42" s="58">
+      <c r="C42" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" s="61">
         <v>46187.0</v>
       </c>
-      <c r="E42" s="59">
+      <c r="E42" s="62">
         <v>0.6666666666666666</v>
       </c>
-      <c r="F42" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="G42" s="9"/>
-      <c r="H42" s="60" t="s">
+      <c r="F42" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="I42" s="9"/>
-      <c r="J42" s="60" t="s">
-        <v>88</v>
-      </c>
-      <c r="K42" s="60" t="s">
+      <c r="G42" s="11"/>
+      <c r="H42" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="I42" s="11"/>
+      <c r="J42" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="L42" s="10"/>
-      <c r="M42" s="61">
+      <c r="K42" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="L42" s="12"/>
+      <c r="M42" s="64">
         <v>23.0</v>
       </c>
-      <c r="N42" s="62" t="s">
-        <v>36</v>
-      </c>
-      <c r="O42" s="63">
+      <c r="N42" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="O42" s="66">
         <v>46190.0</v>
       </c>
-      <c r="P42" s="64">
+      <c r="P42" s="67">
         <v>0.7916666666666666</v>
       </c>
-      <c r="Q42" s="65" t="s">
-        <v>104</v>
-      </c>
-      <c r="R42" s="9"/>
-      <c r="S42" s="65" t="s">
+      <c r="Q42" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="T42" s="9"/>
-      <c r="U42" s="65" t="s">
-        <v>44</v>
-      </c>
-      <c r="V42" s="65" t="s">
+      <c r="R42" s="11"/>
+      <c r="S42" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="T42" s="11"/>
+      <c r="U42" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="W42" s="1"/>
+      <c r="V42" s="68" t="s">
+        <v>46</v>
+      </c>
+      <c r="W42" s="3"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="1"/>
-      <c r="B43" s="56">
+      <c r="A43" s="3"/>
+      <c r="B43" s="59">
         <v>12.0</v>
       </c>
-      <c r="C43" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="D43" s="58">
+      <c r="C43" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" s="61">
         <v>46187.0</v>
       </c>
-      <c r="E43" s="59">
+      <c r="E43" s="62">
         <v>0.9166666666666666</v>
       </c>
-      <c r="F43" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="G43" s="9"/>
-      <c r="H43" s="60" t="s">
+      <c r="F43" s="63" t="s">
         <v>107</v>
       </c>
-      <c r="I43" s="9"/>
-      <c r="J43" s="60" t="s">
-        <v>38</v>
-      </c>
-      <c r="K43" s="60" t="s">
+      <c r="G43" s="11"/>
+      <c r="H43" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="I43" s="11"/>
+      <c r="J43" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="L43" s="10"/>
-      <c r="M43" s="61">
+      <c r="K43" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="L43" s="12"/>
+      <c r="M43" s="64">
         <v>22.0</v>
       </c>
-      <c r="N43" s="62" t="s">
-        <v>36</v>
-      </c>
-      <c r="O43" s="63">
+      <c r="N43" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="O43" s="66">
         <v>46190.0</v>
       </c>
-      <c r="P43" s="64">
+      <c r="P43" s="67">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Q43" s="65" t="s">
-        <v>108</v>
-      </c>
-      <c r="R43" s="9"/>
-      <c r="S43" s="65" t="s">
+      <c r="Q43" s="68" t="s">
         <v>109</v>
       </c>
-      <c r="T43" s="9"/>
-      <c r="U43" s="65" t="s">
-        <v>88</v>
-      </c>
-      <c r="V43" s="65" t="s">
+      <c r="R43" s="11"/>
+      <c r="S43" s="68" t="s">
+        <v>110</v>
+      </c>
+      <c r="T43" s="11"/>
+      <c r="U43" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="W43" s="1"/>
+      <c r="V43" s="68" t="s">
+        <v>90</v>
+      </c>
+      <c r="W43" s="3"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="56">
+      <c r="A44" s="3"/>
+      <c r="B44" s="59">
         <v>34.0</v>
       </c>
-      <c r="C44" s="57" t="s">
-        <v>50</v>
-      </c>
-      <c r="D44" s="58">
+      <c r="C44" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="D44" s="61">
         <v>46193.0</v>
       </c>
-      <c r="E44" s="59">
+      <c r="E44" s="62">
         <v>0.5416666666666666</v>
       </c>
-      <c r="F44" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="G44" s="9"/>
-      <c r="H44" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="I44" s="9"/>
-      <c r="J44" s="60" t="s">
-        <v>57</v>
-      </c>
-      <c r="K44" s="60" t="s">
+      <c r="F44" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="G44" s="11"/>
+      <c r="H44" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="I44" s="11"/>
+      <c r="J44" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="L44" s="10"/>
-      <c r="M44" s="61">
+      <c r="K44" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="12"/>
+      <c r="M44" s="64">
         <v>46.0</v>
       </c>
-      <c r="N44" s="62" t="s">
+      <c r="N44" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="O44" s="66">
+        <v>46196.0</v>
+      </c>
+      <c r="P44" s="67">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="Q44" s="68" t="s">
+        <v>109</v>
+      </c>
+      <c r="R44" s="11"/>
+      <c r="S44" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="T44" s="11"/>
+      <c r="U44" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="V44" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="O44" s="63">
-        <v>46196.0</v>
-      </c>
-      <c r="P44" s="64">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="Q44" s="65" t="s">
-        <v>108</v>
-      </c>
-      <c r="R44" s="9"/>
-      <c r="S44" s="65" t="s">
-        <v>104</v>
-      </c>
-      <c r="T44" s="9"/>
-      <c r="U44" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="V44" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="W44" s="1"/>
+      <c r="W44" s="3"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="1"/>
-      <c r="B45" s="56">
+      <c r="A45" s="3"/>
+      <c r="B45" s="59">
         <v>33.0</v>
       </c>
-      <c r="C45" s="57" t="s">
-        <v>50</v>
-      </c>
-      <c r="D45" s="58">
+      <c r="C45" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45" s="61">
         <v>46193.0</v>
       </c>
-      <c r="E45" s="59">
+      <c r="E45" s="62">
         <v>0.0</v>
       </c>
-      <c r="F45" s="60" t="s">
-        <v>107</v>
-      </c>
-      <c r="G45" s="9"/>
-      <c r="H45" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="I45" s="9"/>
-      <c r="J45" s="60" t="s">
-        <v>38</v>
-      </c>
-      <c r="K45" s="60" t="s">
+      <c r="F45" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="G45" s="11"/>
+      <c r="H45" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="I45" s="11"/>
+      <c r="J45" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="L45" s="10"/>
-      <c r="M45" s="61">
+      <c r="K45" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="L45" s="12"/>
+      <c r="M45" s="64">
         <v>47.0</v>
       </c>
-      <c r="N45" s="62" t="s">
-        <v>65</v>
-      </c>
-      <c r="O45" s="63">
+      <c r="N45" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="O45" s="66">
         <v>46196.0</v>
       </c>
-      <c r="P45" s="64">
+      <c r="P45" s="67">
         <v>0.7916666666666666</v>
       </c>
-      <c r="Q45" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="R45" s="9"/>
-      <c r="S45" s="65" t="s">
-        <v>109</v>
-      </c>
-      <c r="T45" s="9"/>
-      <c r="U45" s="65" t="s">
-        <v>44</v>
-      </c>
-      <c r="V45" s="65" t="s">
+      <c r="Q45" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="R45" s="11"/>
+      <c r="S45" s="68" t="s">
+        <v>110</v>
+      </c>
+      <c r="T45" s="11"/>
+      <c r="U45" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="W45" s="1"/>
+      <c r="V45" s="68" t="s">
+        <v>46</v>
+      </c>
+      <c r="W45" s="3"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="B46" s="56">
+      <c r="A46" s="3"/>
+      <c r="B46" s="59">
         <v>57.0</v>
       </c>
-      <c r="C46" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="58">
+      <c r="C46" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="61">
         <v>46198.0</v>
       </c>
-      <c r="E46" s="59">
+      <c r="E46" s="62">
         <v>0.7916666666666666</v>
       </c>
-      <c r="F46" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="G46" s="9"/>
-      <c r="H46" s="60" t="s">
+      <c r="F46" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="G46" s="11"/>
+      <c r="H46" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="I46" s="11"/>
+      <c r="J46" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="K46" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="L46" s="12"/>
+      <c r="M46" s="64">
+        <v>67.0</v>
+      </c>
+      <c r="N46" s="65" t="s">
+        <v>51</v>
+      </c>
+      <c r="O46" s="66">
+        <v>46200.0</v>
+      </c>
+      <c r="P46" s="67">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="Q46" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="I46" s="9"/>
-      <c r="J46" s="60" t="s">
-        <v>88</v>
-      </c>
-      <c r="K46" s="60" t="s">
-        <v>89</v>
-      </c>
-      <c r="L46" s="10"/>
-      <c r="M46" s="61">
-        <v>67.0</v>
-      </c>
-      <c r="N46" s="62" t="s">
-        <v>50</v>
-      </c>
-      <c r="O46" s="63">
-        <v>46200.0</v>
-      </c>
-      <c r="P46" s="64">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="Q46" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="R46" s="9"/>
-      <c r="S46" s="65" t="s">
-        <v>108</v>
-      </c>
-      <c r="T46" s="9"/>
-      <c r="U46" s="65" t="s">
-        <v>110</v>
-      </c>
-      <c r="V46" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="W46" s="1"/>
+      <c r="R46" s="11"/>
+      <c r="S46" s="68" t="s">
+        <v>109</v>
+      </c>
+      <c r="T46" s="11"/>
+      <c r="U46" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="V46" s="68" t="s">
+        <v>70</v>
+      </c>
+      <c r="W46" s="3"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="1"/>
-      <c r="B47" s="56">
+      <c r="A47" s="3"/>
+      <c r="B47" s="59">
         <v>58.0</v>
       </c>
-      <c r="C47" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="D47" s="58">
+      <c r="C47" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" s="61">
         <v>46198.0</v>
       </c>
-      <c r="E47" s="59">
+      <c r="E47" s="62">
         <v>0.7916666666666666</v>
       </c>
-      <c r="F47" s="60" t="s">
-        <v>107</v>
-      </c>
-      <c r="G47" s="9"/>
-      <c r="H47" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="I47" s="9"/>
-      <c r="J47" s="60" t="s">
-        <v>82</v>
-      </c>
-      <c r="K47" s="60" t="s">
+      <c r="F47" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="G47" s="11"/>
+      <c r="H47" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="I47" s="11"/>
+      <c r="J47" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="L47" s="10"/>
-      <c r="M47" s="61">
+      <c r="K47" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="L47" s="12"/>
+      <c r="M47" s="64">
         <v>68.0</v>
       </c>
-      <c r="N47" s="62" t="s">
-        <v>50</v>
-      </c>
-      <c r="O47" s="63">
+      <c r="N47" s="65" t="s">
+        <v>51</v>
+      </c>
+      <c r="O47" s="66">
         <v>46200.0</v>
       </c>
-      <c r="P47" s="64">
+      <c r="P47" s="67">
         <v>0.7083333333333334</v>
       </c>
-      <c r="Q47" s="65" t="s">
-        <v>109</v>
-      </c>
-      <c r="R47" s="9"/>
-      <c r="S47" s="65" t="s">
-        <v>104</v>
-      </c>
-      <c r="T47" s="9"/>
-      <c r="U47" s="65" t="s">
-        <v>74</v>
-      </c>
-      <c r="V47" s="65" t="s">
+      <c r="Q47" s="68" t="s">
+        <v>110</v>
+      </c>
+      <c r="R47" s="11"/>
+      <c r="S47" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="T47" s="11"/>
+      <c r="U47" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="W47" s="1"/>
+      <c r="V47" s="68" t="s">
+        <v>76</v>
+      </c>
+      <c r="W47" s="3"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
-      <c r="Q48" s="1"/>
-      <c r="R48" s="1"/>
-      <c r="S48" s="1"/>
-      <c r="T48" s="1"/>
-      <c r="U48" s="1"/>
-      <c r="V48" s="1"/>
-      <c r="W48" s="1"/>
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3"/>
+      <c r="S48" s="3"/>
+      <c r="T48" s="3"/>
+      <c r="U48" s="3"/>
+      <c r="V48" s="3"/>
+      <c r="W48" s="3"/>
     </row>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
